--- a/Output Files Qwen3.5 9B/LLM-Parameterized_Reference_Scoring_results_run_01.xlsx
+++ b/Output Files Qwen3.5 9B/LLM-Parameterized_Reference_Scoring_results_run_01.xlsx
@@ -39077,7 +39077,7 @@
         <v>1</v>
       </c>
       <c r="AD407" t="n">
-        <v>0.7729999999999999</v>
+        <v>0.773</v>
       </c>
     </row>
     <row r="408">
@@ -39359,7 +39359,7 @@
         <v>2</v>
       </c>
       <c r="AD410" t="n">
-        <v>0.7959999999999999</v>
+        <v>0.796</v>
       </c>
     </row>
     <row r="411">
@@ -39547,7 +39547,7 @@
         <v>3</v>
       </c>
       <c r="AD412" t="n">
-        <v>0.7234999999999999</v>
+        <v>0.7235</v>
       </c>
     </row>
     <row r="413">
@@ -39829,7 +39829,7 @@
         <v>3</v>
       </c>
       <c r="AD415" t="n">
-        <v>0.7509999999999999</v>
+        <v>0.751</v>
       </c>
     </row>
     <row r="416">
@@ -40487,7 +40487,7 @@
         <v>1</v>
       </c>
       <c r="AD422" t="n">
-        <v>0.6469999999999999</v>
+        <v>0.647</v>
       </c>
     </row>
     <row r="423">
@@ -40572,7 +40572,7 @@
         <v>0.58</v>
       </c>
       <c r="AA423" t="n">
-        <v>0.89</v>
+        <v>0.93</v>
       </c>
       <c r="AB423" t="n">
         <v>0.52</v>
@@ -40581,7 +40581,7 @@
         <v>2</v>
       </c>
       <c r="AD423" t="n">
-        <v>0.597</v>
+        <v>0.605</v>
       </c>
     </row>
     <row r="424">
@@ -40666,7 +40666,7 @@
         <v>0.38</v>
       </c>
       <c r="AA424" t="n">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="AB424" t="n">
         <v>0.67</v>
@@ -40675,7 +40675,7 @@
         <v>3</v>
       </c>
       <c r="AD424" t="n">
-        <v>0.4625</v>
+        <v>0.4805</v>
       </c>
     </row>
     <row r="425">
@@ -40957,7 +40957,7 @@
         <v>3</v>
       </c>
       <c r="AD427" t="n">
-        <v>0.7064999999999999</v>
+        <v>0.7065</v>
       </c>
     </row>
     <row r="428">
@@ -41051,7 +41051,7 @@
         <v>1</v>
       </c>
       <c r="AD428" t="n">
-        <v>0.7729999999999999</v>
+        <v>0.773</v>
       </c>
     </row>
     <row r="429">
@@ -41230,7 +41230,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AA430" t="n">
-        <v>0.89</v>
+        <v>0.93</v>
       </c>
       <c r="AB430" t="n">
         <v>0.52</v>
@@ -41239,7 +41239,7 @@
         <v>3</v>
       </c>
       <c r="AD430" t="n">
-        <v>0.6775</v>
+        <v>0.6855</v>
       </c>
     </row>
     <row r="431">
@@ -41427,7 +41427,7 @@
         <v>2</v>
       </c>
       <c r="AD432" t="n">
-        <v>0.7129999999999999</v>
+        <v>0.713</v>
       </c>
     </row>
     <row r="433">
@@ -41606,7 +41606,7 @@
         <v>0.64</v>
       </c>
       <c r="AA434" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AB434" t="n">
         <v>0.46</v>
@@ -41615,7 +41615,7 @@
         <v>1</v>
       </c>
       <c r="AD434" t="n">
-        <v>0.6240000000000001</v>
+        <v>0.626</v>
       </c>
     </row>
     <row r="435">
@@ -41700,7 +41700,7 @@
         <v>0.38</v>
       </c>
       <c r="AA435" t="n">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="AB435" t="n">
         <v>0.67</v>
@@ -41709,7 +41709,7 @@
         <v>2</v>
       </c>
       <c r="AD435" t="n">
-        <v>0.4625</v>
+        <v>0.4805</v>
       </c>
     </row>
     <row r="436">
@@ -41794,7 +41794,7 @@
         <v>0.13</v>
       </c>
       <c r="AA436" t="n">
-        <v>0.45</v>
+        <v>0.58</v>
       </c>
       <c r="AB436" t="n">
         <v>0.48</v>
@@ -41803,7 +41803,7 @@
         <v>3</v>
       </c>
       <c r="AD436" t="n">
-        <v>0.2075</v>
+        <v>0.2335</v>
       </c>
     </row>
     <row r="437">
@@ -42179,7 +42179,7 @@
         <v>1</v>
       </c>
       <c r="AD440" t="n">
-        <v>0.6469999999999999</v>
+        <v>0.647</v>
       </c>
     </row>
     <row r="441">
@@ -42264,7 +42264,7 @@
         <v>0.51</v>
       </c>
       <c r="AA441" t="n">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="AB441" t="n">
         <v>0.57</v>
@@ -42273,7 +42273,7 @@
         <v>2</v>
       </c>
       <c r="AD441" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.574</v>
       </c>
     </row>
     <row r="442">
@@ -42358,7 +42358,7 @@
         <v>0.19</v>
       </c>
       <c r="AA442" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="AB442" t="n">
         <v>0.52</v>
@@ -42367,7 +42367,7 @@
         <v>3</v>
       </c>
       <c r="AD442" t="n">
-        <v>0.2575</v>
+        <v>0.2815</v>
       </c>
     </row>
     <row r="443">
@@ -42555,7 +42555,7 @@
         <v>2</v>
       </c>
       <c r="AD444" t="n">
-        <v>0.6839999999999999</v>
+        <v>0.6840000000000001</v>
       </c>
     </row>
     <row r="445">
@@ -42743,7 +42743,7 @@
         <v>1</v>
       </c>
       <c r="AD446" t="n">
-        <v>0.6469999999999999</v>
+        <v>0.647</v>
       </c>
     </row>
     <row r="447">
@@ -42828,7 +42828,7 @@
         <v>0.51</v>
       </c>
       <c r="AA447" t="n">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="AB447" t="n">
         <v>0.57</v>
@@ -42837,7 +42837,7 @@
         <v>2</v>
       </c>
       <c r="AD447" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.574</v>
       </c>
     </row>
     <row r="448">
@@ -42922,7 +42922,7 @@
         <v>0.19</v>
       </c>
       <c r="AA448" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="AB448" t="n">
         <v>0.52</v>
@@ -42931,7 +42931,7 @@
         <v>3</v>
       </c>
       <c r="AD448" t="n">
-        <v>0.2575</v>
+        <v>0.2815</v>
       </c>
     </row>
     <row r="449">
@@ -43298,7 +43298,7 @@
         <v>0.38</v>
       </c>
       <c r="AA452" t="n">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="AB452" t="n">
         <v>0.67</v>
@@ -43307,7 +43307,7 @@
         <v>1</v>
       </c>
       <c r="AD452" t="n">
-        <v>0.4625</v>
+        <v>0.4805</v>
       </c>
     </row>
     <row r="453">
@@ -43392,7 +43392,7 @@
         <v>0.19</v>
       </c>
       <c r="AA453" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="AB453" t="n">
         <v>0.52</v>
@@ -43401,7 +43401,7 @@
         <v>2</v>
       </c>
       <c r="AD453" t="n">
-        <v>0.2575</v>
+        <v>0.2815</v>
       </c>
     </row>
     <row r="454">
@@ -43486,7 +43486,7 @@
         <v>0</v>
       </c>
       <c r="AA454" t="n">
-        <v>0.21</v>
+        <v>0.36</v>
       </c>
       <c r="AB454" t="n">
         <v>0.4</v>
@@ -43495,7 +43495,7 @@
         <v>3</v>
       </c>
       <c r="AD454" t="n">
-        <v>0.102</v>
+        <v>0.132</v>
       </c>
     </row>
     <row r="455">
@@ -43683,7 +43683,7 @@
         <v>1</v>
       </c>
       <c r="AD456" t="n">
-        <v>0.8190000000000001</v>
+        <v>0.819</v>
       </c>
     </row>
     <row r="457">
@@ -43777,7 +43777,7 @@
         <v>3</v>
       </c>
       <c r="AD457" t="n">
-        <v>0.6715000000000001</v>
+        <v>0.6715</v>
       </c>
     </row>
     <row r="458">
@@ -44153,7 +44153,7 @@
         <v>3</v>
       </c>
       <c r="AD461" t="n">
-        <v>0.7084999999999999</v>
+        <v>0.7085</v>
       </c>
     </row>
     <row r="462">
@@ -44247,7 +44247,7 @@
         <v>1</v>
       </c>
       <c r="AD462" t="n">
-        <v>0.7729999999999999</v>
+        <v>0.773</v>
       </c>
     </row>
     <row r="463">
@@ -44623,7 +44623,7 @@
         <v>3</v>
       </c>
       <c r="AD466" t="n">
-        <v>0.7129999999999999</v>
+        <v>0.713</v>
       </c>
     </row>
     <row r="467">
@@ -44708,7 +44708,7 @@
         <v>0.64</v>
       </c>
       <c r="AA467" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AB467" t="n">
         <v>0.46</v>
@@ -44717,7 +44717,7 @@
         <v>1</v>
       </c>
       <c r="AD467" t="n">
-        <v>0.6240000000000001</v>
+        <v>0.626</v>
       </c>
     </row>
     <row r="468">
@@ -44802,7 +44802,7 @@
         <v>0.38</v>
       </c>
       <c r="AA468" t="n">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="AB468" t="n">
         <v>0.67</v>
@@ -44811,7 +44811,7 @@
         <v>2</v>
       </c>
       <c r="AD468" t="n">
-        <v>0.4625</v>
+        <v>0.4805</v>
       </c>
     </row>
     <row r="469">
@@ -44896,7 +44896,7 @@
         <v>0.19</v>
       </c>
       <c r="AA469" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="AB469" t="n">
         <v>0.52</v>
@@ -44905,7 +44905,7 @@
         <v>3</v>
       </c>
       <c r="AD469" t="n">
-        <v>0.2575</v>
+        <v>0.2815</v>
       </c>
     </row>
     <row r="470">
@@ -45093,7 +45093,7 @@
         <v>1</v>
       </c>
       <c r="AD471" t="n">
-        <v>0.8190000000000001</v>
+        <v>0.819</v>
       </c>
     </row>
     <row r="472">
@@ -45187,7 +45187,7 @@
         <v>3</v>
       </c>
       <c r="AD472" t="n">
-        <v>0.6715000000000001</v>
+        <v>0.6715</v>
       </c>
     </row>
     <row r="473">
@@ -45375,7 +45375,7 @@
         <v>2</v>
       </c>
       <c r="AD474" t="n">
-        <v>0.6260000000000001</v>
+        <v>0.626</v>
       </c>
     </row>
     <row r="475">
@@ -45563,7 +45563,7 @@
         <v>1</v>
       </c>
       <c r="AD476" t="n">
-        <v>0.7615000000000001</v>
+        <v>0.7615</v>
       </c>
     </row>
     <row r="477">
@@ -45939,7 +45939,7 @@
         <v>2</v>
       </c>
       <c r="AD480" t="n">
-        <v>0.6729999999999999</v>
+        <v>0.673</v>
       </c>
     </row>
     <row r="481">
@@ -46024,7 +46024,7 @@
         <v>0.51</v>
       </c>
       <c r="AA481" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="AB481" t="n">
         <v>0.57</v>
@@ -46033,7 +46033,7 @@
         <v>3</v>
       </c>
       <c r="AD481" t="n">
-        <v>0.6020000000000001</v>
+        <v>0.614</v>
       </c>
     </row>
     <row r="482">
@@ -46127,7 +46127,7 @@
         <v>1</v>
       </c>
       <c r="AD482" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="483">
@@ -46221,7 +46221,7 @@
         <v>2</v>
       </c>
       <c r="AD483" t="n">
-        <v>0.7370000000000001</v>
+        <v>0.737</v>
       </c>
     </row>
     <row r="484">
@@ -46306,7 +46306,7 @@
         <v>0.38</v>
       </c>
       <c r="AA484" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="AB484" t="n">
         <v>0.52</v>
@@ -46315,7 +46315,7 @@
         <v>3</v>
       </c>
       <c r="AD484" t="n">
-        <v>0.447</v>
+        <v>0.461</v>
       </c>
     </row>
     <row r="485">
@@ -46409,7 +46409,7 @@
         <v>1</v>
       </c>
       <c r="AD485" t="n">
-        <v>0.7555000000000001</v>
+        <v>0.7554999999999999</v>
       </c>
     </row>
     <row r="486">
@@ -46776,7 +46776,7 @@
         <v>0.54</v>
       </c>
       <c r="AA489" t="n">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="AB489" t="n">
         <v>0.67</v>
@@ -46785,7 +46785,7 @@
         <v>2</v>
       </c>
       <c r="AD489" t="n">
-        <v>0.6035</v>
+        <v>0.6175</v>
       </c>
     </row>
     <row r="490">
@@ -46870,7 +46870,7 @@
         <v>0.13</v>
       </c>
       <c r="AA490" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AB490" t="n">
         <v>0.32</v>
@@ -46879,7 +46879,7 @@
         <v>3</v>
       </c>
       <c r="AD490" t="n">
-        <v>0.1235</v>
+        <v>0.1355</v>
       </c>
     </row>
     <row r="491">
@@ -46973,7 +46973,7 @@
         <v>1</v>
       </c>
       <c r="AD491" t="n">
-        <v>0.7084999999999999</v>
+        <v>0.7085</v>
       </c>
     </row>
     <row r="492">
@@ -47161,7 +47161,7 @@
         <v>3</v>
       </c>
       <c r="AD493" t="n">
-        <v>0.3995000000000001</v>
+        <v>0.3995</v>
       </c>
     </row>
     <row r="494">
@@ -47349,7 +47349,7 @@
         <v>2</v>
       </c>
       <c r="AD495" t="n">
-        <v>0.7174999999999999</v>
+        <v>0.7175</v>
       </c>
     </row>
     <row r="496">
@@ -47725,7 +47725,7 @@
         <v>3</v>
       </c>
       <c r="AD499" t="n">
-        <v>0.6365000000000001</v>
+        <v>0.6365</v>
       </c>
     </row>
     <row r="500">
@@ -48289,7 +48289,7 @@
         <v>3</v>
       </c>
       <c r="AD505" t="n">
-        <v>0.6465000000000001</v>
+        <v>0.6465</v>
       </c>
     </row>
     <row r="506">
@@ -48750,7 +48750,7 @@
         <v>0.64</v>
       </c>
       <c r="AA510" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AB510" t="n">
         <v>0.46</v>
@@ -48759,7 +48759,7 @@
         <v>2</v>
       </c>
       <c r="AD510" t="n">
-        <v>0.6519999999999999</v>
+        <v>0.654</v>
       </c>
     </row>
     <row r="511">
@@ -48844,7 +48844,7 @@
         <v>0.38</v>
       </c>
       <c r="AA511" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="AB511" t="n">
         <v>0.67</v>
@@ -48853,7 +48853,7 @@
         <v>3</v>
       </c>
       <c r="AD511" t="n">
-        <v>0.4965000000000001</v>
+        <v>0.5125</v>
       </c>
     </row>
     <row r="512">
@@ -48938,7 +48938,7 @@
         <v>0.64</v>
       </c>
       <c r="AA512" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AB512" t="n">
         <v>0.46</v>
@@ -48947,7 +48947,7 @@
         <v>1</v>
       </c>
       <c r="AD512" t="n">
-        <v>0.665</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="513">
@@ -49032,7 +49032,7 @@
         <v>0.51</v>
       </c>
       <c r="AA513" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="AB513" t="n">
         <v>0.57</v>
@@ -49041,7 +49041,7 @@
         <v>2</v>
       </c>
       <c r="AD513" t="n">
-        <v>0.6020000000000001</v>
+        <v>0.614</v>
       </c>
     </row>
     <row r="514">
@@ -49126,7 +49126,7 @@
         <v>0.38</v>
       </c>
       <c r="AA514" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="AB514" t="n">
         <v>0.67</v>
@@ -49135,7 +49135,7 @@
         <v>3</v>
       </c>
       <c r="AD514" t="n">
-        <v>0.5065000000000001</v>
+        <v>0.5185</v>
       </c>
     </row>
     <row r="515">
@@ -49314,7 +49314,7 @@
         <v>0.51</v>
       </c>
       <c r="AA516" t="n">
-        <v>0.92</v>
+        <v>0.99</v>
       </c>
       <c r="AB516" t="n">
         <v>0.57</v>
@@ -49323,7 +49323,7 @@
         <v>2</v>
       </c>
       <c r="AD516" t="n">
-        <v>0.5950000000000001</v>
+        <v>0.609</v>
       </c>
     </row>
     <row r="517">
@@ -49408,7 +49408,7 @@
         <v>0.38</v>
       </c>
       <c r="AA517" t="n">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="AB517" t="n">
         <v>0.67</v>
@@ -49417,7 +49417,7 @@
         <v>3</v>
       </c>
       <c r="AD517" t="n">
-        <v>0.4995000000000001</v>
+        <v>0.5135</v>
       </c>
     </row>
     <row r="518">
@@ -49502,7 +49502,7 @@
         <v>0.64</v>
       </c>
       <c r="AA518" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AB518" t="n">
         <v>0.46</v>
@@ -49511,7 +49511,7 @@
         <v>1</v>
       </c>
       <c r="AD518" t="n">
-        <v>0.6779999999999999</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="519">
@@ -49596,7 +49596,7 @@
         <v>0.51</v>
       </c>
       <c r="AA519" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="AB519" t="n">
         <v>0.57</v>
@@ -49605,7 +49605,7 @@
         <v>2</v>
       </c>
       <c r="AD519" t="n">
-        <v>0.6090000000000001</v>
+        <v>0.619</v>
       </c>
     </row>
     <row r="520">
@@ -49690,7 +49690,7 @@
         <v>0.38</v>
       </c>
       <c r="AA520" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="AB520" t="n">
         <v>0.67</v>
@@ -49699,7 +49699,7 @@
         <v>3</v>
       </c>
       <c r="AD520" t="n">
-        <v>0.5185000000000001</v>
+        <v>0.5265</v>
       </c>
     </row>
     <row r="521">
@@ -49784,7 +49784,7 @@
         <v>0.74</v>
       </c>
       <c r="AA521" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AB521" t="n">
         <v>0.46</v>
@@ -49793,7 +49793,7 @@
         <v>1</v>
       </c>
       <c r="AD521" t="n">
-        <v>0.73</v>
+        <v>0.732</v>
       </c>
     </row>
     <row r="522">
@@ -49878,7 +49878,7 @@
         <v>0.64</v>
       </c>
       <c r="AA522" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="AB522" t="n">
         <v>0.57</v>
@@ -49887,7 +49887,7 @@
         <v>2</v>
       </c>
       <c r="AD522" t="n">
-        <v>0.6835</v>
+        <v>0.6955</v>
       </c>
     </row>
     <row r="523">
@@ -49972,7 +49972,7 @@
         <v>0.54</v>
       </c>
       <c r="AA523" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="AB523" t="n">
         <v>0.67</v>
@@ -49981,7 +49981,7 @@
         <v>3</v>
       </c>
       <c r="AD523" t="n">
-        <v>0.6075</v>
+        <v>0.6195000000000001</v>
       </c>
     </row>
     <row r="524">
@@ -50160,7 +50160,7 @@
         <v>0.51</v>
       </c>
       <c r="AA525" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="AB525" t="n">
         <v>0.57</v>
@@ -50169,7 +50169,7 @@
         <v>2</v>
       </c>
       <c r="AD525" t="n">
-        <v>0.6080000000000001</v>
+        <v>0.616</v>
       </c>
     </row>
     <row r="526">
@@ -50254,7 +50254,7 @@
         <v>0.38</v>
       </c>
       <c r="AA526" t="n">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="AB526" t="n">
         <v>0.67</v>
@@ -50263,7 +50263,7 @@
         <v>3</v>
       </c>
       <c r="AD526" t="n">
-        <v>0.5155000000000001</v>
+        <v>0.5255</v>
       </c>
     </row>
     <row r="527">
@@ -50451,7 +50451,7 @@
         <v>2</v>
       </c>
       <c r="AD528" t="n">
-        <v>0.6260000000000001</v>
+        <v>0.626</v>
       </c>
     </row>
     <row r="529">
@@ -51015,7 +51015,7 @@
         <v>2</v>
       </c>
       <c r="AD534" t="n">
-        <v>0.6260000000000001</v>
+        <v>0.626</v>
       </c>
     </row>
     <row r="535">
@@ -51297,7 +51297,7 @@
         <v>2</v>
       </c>
       <c r="AD537" t="n">
-        <v>0.7149999999999999</v>
+        <v>0.715</v>
       </c>
     </row>
     <row r="538">
@@ -51485,7 +51485,7 @@
         <v>1</v>
       </c>
       <c r="AD539" t="n">
-        <v>0.7344999999999999</v>
+        <v>0.7345</v>
       </c>
     </row>
     <row r="540">
@@ -51946,7 +51946,7 @@
         <v>0.51</v>
       </c>
       <c r="AA544" t="n">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="AB544" t="n">
         <v>0.57</v>
@@ -51955,7 +51955,7 @@
         <v>3</v>
       </c>
       <c r="AD544" t="n">
-        <v>0.5720000000000001</v>
+        <v>0.586</v>
       </c>
     </row>
     <row r="545">
@@ -52049,7 +52049,7 @@
         <v>2</v>
       </c>
       <c r="AD545" t="n">
-        <v>0.6764999999999999</v>
+        <v>0.6765</v>
       </c>
     </row>
     <row r="546">
@@ -52331,7 +52331,7 @@
         <v>1</v>
       </c>
       <c r="AD548" t="n">
-        <v>0.7374999999999999</v>
+        <v>0.7375</v>
       </c>
     </row>
     <row r="549">
@@ -53083,7 +53083,7 @@
         <v>3</v>
       </c>
       <c r="AD556" t="n">
-        <v>0.5455000000000001</v>
+        <v>0.5455</v>
       </c>
     </row>
     <row r="557">
@@ -53177,7 +53177,7 @@
         <v>1</v>
       </c>
       <c r="AD557" t="n">
-        <v>0.6769999999999999</v>
+        <v>0.677</v>
       </c>
     </row>
     <row r="558">
@@ -53262,7 +53262,7 @@
         <v>0.64</v>
       </c>
       <c r="AA558" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AB558" t="n">
         <v>0.46</v>
@@ -53271,7 +53271,7 @@
         <v>2</v>
       </c>
       <c r="AD558" t="n">
-        <v>0.665</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="559">
@@ -53356,7 +53356,7 @@
         <v>0.51</v>
       </c>
       <c r="AA559" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="AB559" t="n">
         <v>0.57</v>
@@ -53365,7 +53365,7 @@
         <v>3</v>
       </c>
       <c r="AD559" t="n">
-        <v>0.6020000000000001</v>
+        <v>0.614</v>
       </c>
     </row>
     <row r="560">
@@ -53544,7 +53544,7 @@
         <v>0.51</v>
       </c>
       <c r="AA561" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="AB561" t="n">
         <v>0.57</v>
@@ -53553,7 +53553,7 @@
         <v>2</v>
       </c>
       <c r="AD561" t="n">
-        <v>0.6080000000000001</v>
+        <v>0.616</v>
       </c>
     </row>
     <row r="562">
@@ -53638,7 +53638,7 @@
         <v>0.38</v>
       </c>
       <c r="AA562" t="n">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="AB562" t="n">
         <v>0.67</v>
@@ -53647,7 +53647,7 @@
         <v>3</v>
       </c>
       <c r="AD562" t="n">
-        <v>0.5155000000000001</v>
+        <v>0.5255</v>
       </c>
     </row>
     <row r="563">
@@ -54023,7 +54023,7 @@
         <v>2</v>
       </c>
       <c r="AD566" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="567">
@@ -54117,7 +54117,7 @@
         <v>3</v>
       </c>
       <c r="AD567" t="n">
-        <v>0.7825000000000001</v>
+        <v>0.7825</v>
       </c>
     </row>
     <row r="568">
@@ -54305,7 +54305,7 @@
         <v>2</v>
       </c>
       <c r="AD569" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="570">
@@ -54587,7 +54587,7 @@
         <v>1</v>
       </c>
       <c r="AD572" t="n">
-        <v>0.7649999999999999</v>
+        <v>0.765</v>
       </c>
     </row>
     <row r="573">
@@ -54775,7 +54775,7 @@
         <v>3</v>
       </c>
       <c r="AD574" t="n">
-        <v>0.7069999999999999</v>
+        <v>0.707</v>
       </c>
     </row>
     <row r="575">
@@ -54869,7 +54869,7 @@
         <v>1</v>
       </c>
       <c r="AD575" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="576">
@@ -55339,7 +55339,7 @@
         <v>3</v>
       </c>
       <c r="AD580" t="n">
-        <v>0.7124999999999999</v>
+        <v>0.7125</v>
       </c>
     </row>
     <row r="581">
